--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T08:49:22+00:00</t>
+    <t>2026-03-04T09:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T09:38:55+00:00</t>
+    <t>2026-03-04T10:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
